--- a/Dodumentacion/GoldBracelets_Sprints_Software2_Grupo2_COMPLETO.xlsx
+++ b/Dodumentacion/GoldBracelets_Sprints_Software2_Grupo2_COMPLETO.xlsx
@@ -2412,7 +2412,7 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>• 24 pruebas automáticas (python manage.py test account)
+          <t>• 30 pruebas automáticas (python manage.py test account)
 • Documentación completa en docs/ y esquema SQL
 • Guía de despliegue y de estudio para la sustentación</t>
         </is>
